--- a/deploy/converter-reference.xlsx
+++ b/deploy/converter-reference.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Счёт" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,14 +16,24 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="DD.MM.YYYY"/>
+  </numFmts>
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +44,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +52,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -412,27 +440,213 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Счёт на оплату № 17</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Счёт на оплату № 17 от 20.02.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Поставщик:</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ООО «Эталон-Снаб», ИНН 7700000017</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Покупатель:</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ООО «Монтаж-Проба», ИНН 7800000025</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Оплатить до:</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Кол-во</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Ед.</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Цена</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Сумма</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Кабель силовой ВВГнг(А)-LS 3х2,5</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>2580</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Коробка распределительная 100х100х50</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>61.44</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>860.16</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Гофра ПВХ диаметром 20 мм с протяжкой</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Итого:</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="n">
         <v>3834.16</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>В том числе НДС 20 %:</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>639.03</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Всего наименований 3, на сумму 3 834 рубля 16 копеек.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Руководитель ______________ Образцов А. А.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A16:C16"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>